--- a/referenceDocument/用例模板.xlsx
+++ b/referenceDocument/用例模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="遂宁城市大脑应用场景-民生场景-全部用例" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>用例编号</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>预期</t>
+  </si>
+  <si>
+    <t>route_path</t>
   </si>
   <si>
     <t xml:space="preserve">7306	</t>
@@ -1234,16 +1237,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9.81481481481481" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
-    <col min="4" max="4" width="33.2727272727273" customWidth="1"/>
-    <col min="5" max="5" width="41.0909090909091" customWidth="1"/>
-    <col min="6" max="6" width="35.5454545454545" customWidth="1"/>
+    <col min="4" max="4" width="33.2685185185185" customWidth="1"/>
+    <col min="5" max="5" width="41.0925925925926" customWidth="1"/>
+    <col min="6" max="6" width="35.5462962962963" customWidth="1"/>
     <col min="7" max="7" width="70" customWidth="1"/>
+    <col min="8" max="8" width="19.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1265,28 +1269,31 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" ht="84" spans="1:7">
+    <row r="2" ht="86.4" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
